--- a/artfynd/A 39528-2025 artfynd.xlsx
+++ b/artfynd/A 39528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61006520</v>
+        <v>61006519</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665984.0373539687</v>
+        <v>666013</v>
       </c>
       <c r="R2" t="n">
-        <v>7174967.319093642</v>
+        <v>7174972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61006522</v>
+        <v>61006523</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665966.5346426698</v>
+        <v>665967</v>
       </c>
       <c r="R3" t="n">
-        <v>7174926.005967917</v>
+        <v>7174926</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61006523</v>
+        <v>61400411</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,14 +905,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>naturskog V Bålforsreservatet, Ly lm</t>
+          <t>skog NV Bålforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665966.5346426698</v>
+        <v>665681</v>
       </c>
       <c r="R4" t="n">
-        <v>7174926.005967917</v>
+        <v>7175349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +958,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>kolad ved</t>
+          <t>kolad stubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61006519</v>
+        <v>61006520</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666012.9881626994</v>
+        <v>665984</v>
       </c>
       <c r="R5" t="n">
-        <v>7174972.343166766</v>
+        <v>7174967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,21 +1044,11 @@
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61400411</v>
+        <v>61400413</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665681.1613780212</v>
+        <v>665680</v>
       </c>
       <c r="R6" t="n">
-        <v>7175349.041160419</v>
+        <v>7175343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,21 +1146,11 @@
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1162,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>kolad stubbe</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61400413</v>
+        <v>61006524</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1191,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>skog NV Bålforsen, Ly lm</t>
+          <t>Bålforsen NR, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665680.1809700986</v>
+        <v>666152</v>
       </c>
       <c r="R7" t="n">
-        <v>7175343.407604323</v>
+        <v>7174887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1269,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1369,6 +1284,108 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61006522</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>naturskog V Bålforsreservatet, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>665967</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174926</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-08-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-08-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>kolad ved</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39528-2025 artfynd.xlsx
+++ b/artfynd/A 39528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61006519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61006523</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61400411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61006520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61400413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61006524</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,8 +1421,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61006522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>